--- a/tests/output/20260218response_small.xlsx
+++ b/tests/output/20260218response_small.xlsx
@@ -49,25 +49,34 @@
     <t>g00576</t>
   </si>
   <si>
+    <t>a00216</t>
+  </si>
+  <si>
+    <t>a00220</t>
+  </si>
+  <si>
+    <t>a00219</t>
+  </si>
+  <si>
+    <t>a00209</t>
+  </si>
+  <si>
     <t>a00205</t>
   </si>
   <si>
-    <t>a00220</t>
+    <t>a00221</t>
   </si>
   <si>
     <t>a00213</t>
   </si>
   <si>
-    <t>a00216</t>
-  </si>
-  <si>
-    <t>a00219</t>
-  </si>
-  <si>
-    <t>a00221</t>
-  </si>
-  <si>
-    <t>a00209</t>
+    <t>a00207</t>
+  </si>
+  <si>
+    <t>a00218</t>
+  </si>
+  <si>
+    <t>a00217</t>
   </si>
   <si>
     <t>a00203</t>
@@ -76,70 +85,61 @@
     <t>a00215</t>
   </si>
   <si>
-    <t>a00207</t>
-  </si>
-  <si>
     <t>a00214</t>
   </si>
   <si>
-    <t>a00217</t>
-  </si>
-  <si>
-    <t>a00218</t>
-  </si>
-  <si>
-    <t>t00044</t>
+    <t>t00181</t>
   </si>
   <si>
     <t>t00256</t>
   </si>
   <si>
-    <t>t00150</t>
-  </si>
-  <si>
-    <t>t00199</t>
-  </si>
-  <si>
-    <t>t00251</t>
-  </si>
-  <si>
-    <t>t00288</t>
-  </si>
-  <si>
-    <t>t00120</t>
-  </si>
-  <si>
-    <t>t00059</t>
-  </si>
-  <si>
-    <t>t00165</t>
-  </si>
-  <si>
-    <t>t00077</t>
-  </si>
-  <si>
-    <t>t00162</t>
-  </si>
-  <si>
-    <t>t00225</t>
-  </si>
-  <si>
-    <t>t00240</t>
+    <t>t00249</t>
+  </si>
+  <si>
+    <t>t00117</t>
+  </si>
+  <si>
+    <t>t00048</t>
+  </si>
+  <si>
+    <t>t00290</t>
+  </si>
+  <si>
+    <t>t00158</t>
+  </si>
+  <si>
+    <t>t00076</t>
+  </si>
+  <si>
+    <t>t00232</t>
+  </si>
+  <si>
+    <t>t00221</t>
+  </si>
+  <si>
+    <t>t00061</t>
+  </si>
+  <si>
+    <t>t00177</t>
+  </si>
+  <si>
+    <t>t00163</t>
+  </si>
+  <si>
+    <t>roskilde</t>
+  </si>
+  <si>
+    <t>ruc</t>
   </si>
   <si>
     <t>lejren</t>
   </si>
   <si>
-    <t>ruc</t>
+    <t>hoje-taastrup</t>
   </si>
   <si>
     <t>veddelev</t>
-  </si>
-  <si>
-    <t>roskilde</t>
-  </si>
-  <si>
-    <t>hoje-taastrup</t>
   </si>
 </sst>
 </file>
@@ -544,19 +544,19 @@
         <v>24</v>
       </c>
       <c r="D2" s="2">
-        <v>46222.47916666666</v>
+        <v>46222.29166666666</v>
       </c>
       <c r="E2" s="2">
-        <v>46222.58333333334</v>
+        <v>46222.41666666666</v>
       </c>
       <c r="F2" t="s">
         <v>37</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -602,19 +602,19 @@
         <v>26</v>
       </c>
       <c r="D4" s="2">
-        <v>46224.47916666666</v>
+        <v>46224.77083333334</v>
       </c>
       <c r="E4" s="2">
-        <v>46224.58333333334</v>
+        <v>46224.83333333334</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -631,19 +631,19 @@
         <v>27</v>
       </c>
       <c r="D5" s="2">
-        <v>46225.47916666666</v>
+        <v>46225.29166666666</v>
       </c>
       <c r="E5" s="2">
-        <v>46225.60416666666</v>
+        <v>46225.375</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -660,19 +660,19 @@
         <v>28</v>
       </c>
       <c r="D6" s="2">
-        <v>46225.79166666666</v>
+        <v>46225.47916666666</v>
       </c>
       <c r="E6" s="2">
-        <v>46225.83333333334</v>
+        <v>46225.58333333334</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -689,13 +689,13 @@
         <v>29</v>
       </c>
       <c r="D7" s="2">
-        <v>46227.29166666666</v>
+        <v>46227.47916666666</v>
       </c>
       <c r="E7" s="2">
-        <v>46227.41666666666</v>
+        <v>46227.60416666666</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -721,16 +721,16 @@
         <v>46228.47916666666</v>
       </c>
       <c r="E8" s="2">
-        <v>46228.5625</v>
+        <v>46228.58333333334</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -747,19 +747,19 @@
         <v>31</v>
       </c>
       <c r="D9" s="2">
-        <v>46222.29166666666</v>
+        <v>46223.77083333334</v>
       </c>
       <c r="E9" s="2">
-        <v>46222.35416666666</v>
+        <v>46223.8125</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -776,19 +776,19 @@
         <v>32</v>
       </c>
       <c r="D10" s="2">
-        <v>46223.47916666666</v>
+        <v>46224.29166666666</v>
       </c>
       <c r="E10" s="2">
-        <v>46223.60416666666</v>
+        <v>46224.41666666666</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H10">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -805,19 +805,19 @@
         <v>33</v>
       </c>
       <c r="D11" s="2">
-        <v>46224.70833333334</v>
+        <v>46224.47916666666</v>
       </c>
       <c r="E11" s="2">
-        <v>46224.75</v>
+        <v>46224.54166666666</v>
       </c>
       <c r="F11" t="s">
         <v>37</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -834,19 +834,19 @@
         <v>34</v>
       </c>
       <c r="D12" s="2">
-        <v>46225.70833333334</v>
+        <v>46225.29166666666</v>
       </c>
       <c r="E12" s="2">
-        <v>46225.75</v>
+        <v>46225.35416666666</v>
       </c>
       <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -866,16 +866,16 @@
         <v>46226.47916666666</v>
       </c>
       <c r="E13" s="2">
-        <v>46226.54166666666</v>
+        <v>46226.60416666666</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -895,16 +895,16 @@
         <v>46226.70833333334</v>
       </c>
       <c r="E14" s="2">
-        <v>46226.83333333334</v>
+        <v>46226.75</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I14">
         <v>1</v>
